--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2531" uniqueCount="1774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2521" uniqueCount="1773">
   <si>
     <t>ID</t>
   </si>
@@ -5317,9 +5317,6 @@
   </si>
   <si>
     <t>74000000000000</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>10240</t>
@@ -24343,38 +24340,34 @@
       </c>
     </row>
     <row r="246" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A246" s="8" t="s">
+      <c r="A246" s="8"/>
+      <c r="B246" s="8"/>
+      <c r="C246" s="45" t="s">
         <v>1743</v>
       </c>
-      <c r="B246" s="8" t="s">
-        <v>1743</v>
-      </c>
-      <c r="C246" s="45" t="s">
+      <c r="D246" s="45" t="s">
         <v>1744</v>
-      </c>
-      <c r="D246" s="45" t="s">
-        <v>1745</v>
       </c>
       <c r="E246" s="7">
         <v>7</v>
       </c>
       <c r="F246" s="7" t="s">
+        <v>1745</v>
+      </c>
+      <c r="G246" s="38" t="s">
         <v>1746</v>
-      </c>
-      <c r="G246" s="38" t="s">
-        <v>1747</v>
       </c>
       <c r="H246" s="44" t="s">
         <v>1281</v>
       </c>
       <c r="I246" s="38" t="s">
+        <v>1747</v>
+      </c>
+      <c r="J246" s="42" t="s">
         <v>1748</v>
       </c>
-      <c r="J246" s="42" t="s">
-        <v>1749</v>
-      </c>
       <c r="K246" s="42" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="L246" s="38" t="s">
         <v>1663</v>
@@ -24411,10 +24404,10 @@
         <v>99.99</v>
       </c>
       <c r="U246" s="43" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="V246" s="43" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="X246" s="3" t="s">
         <v>158</v>
@@ -24424,38 +24417,34 @@
       </c>
     </row>
     <row r="247" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A247" s="8" t="s">
-        <v>1743</v>
-      </c>
-      <c r="B247" s="8" t="s">
-        <v>1743</v>
-      </c>
+      <c r="A247" s="8"/>
+      <c r="B247" s="8"/>
       <c r="C247" s="45" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D247" s="45" t="s">
         <v>1751</v>
-      </c>
-      <c r="D247" s="45" t="s">
-        <v>1752</v>
       </c>
       <c r="E247" s="7">
         <v>7</v>
       </c>
       <c r="F247" s="7" t="s">
+        <v>1752</v>
+      </c>
+      <c r="G247" s="38" t="s">
         <v>1753</v>
-      </c>
-      <c r="G247" s="38" t="s">
-        <v>1754</v>
       </c>
       <c r="H247" s="44" t="s">
         <v>1281</v>
       </c>
       <c r="I247" s="38" t="s">
+        <v>1754</v>
+      </c>
+      <c r="J247" s="42" t="s">
         <v>1755</v>
       </c>
-      <c r="J247" s="42" t="s">
-        <v>1756</v>
-      </c>
       <c r="K247" s="42" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="L247" s="38" t="s">
         <v>1734</v>
@@ -24492,10 +24481,10 @@
         <v>99.99</v>
       </c>
       <c r="U247" s="43" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="V247" s="43" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="X247" s="3" t="s">
         <v>158</v>
@@ -24505,23 +24494,19 @@
       </c>
     </row>
     <row r="248" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A248" s="8" t="s">
-        <v>1743</v>
-      </c>
-      <c r="B248" s="8" t="s">
-        <v>1743</v>
-      </c>
+      <c r="A248" s="8"/>
+      <c r="B248" s="8"/>
       <c r="C248" s="45" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D248" s="45" t="s">
         <v>1758</v>
-      </c>
-      <c r="D248" s="45" t="s">
-        <v>1759</v>
       </c>
       <c r="E248" s="7">
         <v>7</v>
       </c>
       <c r="F248" s="7" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="G248" s="38" t="s">
         <v>1676</v>
@@ -24530,16 +24515,16 @@
         <v>1281</v>
       </c>
       <c r="I248" s="38" t="s">
+        <v>1760</v>
+      </c>
+      <c r="J248" s="42" t="s">
         <v>1761</v>
       </c>
-      <c r="J248" s="42" t="s">
-        <v>1762</v>
-      </c>
       <c r="K248" s="42" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="L248" s="38" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="M248" s="7">
         <f t="shared" si="93"/>
@@ -24586,32 +24571,28 @@
       </c>
     </row>
     <row r="249" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A249" s="8" t="s">
-        <v>1743</v>
-      </c>
-      <c r="B249" s="8" t="s">
-        <v>1743</v>
-      </c>
+      <c r="A249" s="8"/>
+      <c r="B249" s="8"/>
       <c r="C249" s="45" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D249" s="45" t="s">
         <v>1763</v>
-      </c>
-      <c r="D249" s="45" t="s">
-        <v>1764</v>
       </c>
       <c r="E249" s="7">
         <v>7</v>
       </c>
       <c r="F249" s="7" t="s">
+        <v>1764</v>
+      </c>
+      <c r="G249" s="38" t="s">
         <v>1765</v>
-      </c>
-      <c r="G249" s="38" t="s">
-        <v>1766</v>
       </c>
       <c r="H249" s="44" t="s">
         <v>1281</v>
       </c>
       <c r="I249" s="38" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="J249" s="42" t="s">
         <v>1423</v>
@@ -24667,32 +24648,28 @@
       </c>
     </row>
     <row r="250" s="3" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A250" s="8" t="s">
-        <v>1743</v>
-      </c>
-      <c r="B250" s="8" t="s">
-        <v>1743</v>
-      </c>
+      <c r="A250" s="8"/>
+      <c r="B250" s="8"/>
       <c r="C250" s="45" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D250" s="45" t="s">
         <v>1768</v>
-      </c>
-      <c r="D250" s="45" t="s">
-        <v>1769</v>
       </c>
       <c r="E250" s="7">
         <v>7</v>
       </c>
       <c r="F250" s="7" t="s">
+        <v>1769</v>
+      </c>
+      <c r="G250" s="38" t="s">
         <v>1770</v>
-      </c>
-      <c r="G250" s="38" t="s">
-        <v>1771</v>
       </c>
       <c r="H250" s="44" t="s">
         <v>1281</v>
       </c>
       <c r="I250" s="38" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="J250" s="42" t="s">
         <v>1576</v>
@@ -24701,7 +24678,7 @@
         <v>1576</v>
       </c>
       <c r="L250" s="38" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="M250" s="7">
         <f t="shared" si="93"/>
@@ -24735,10 +24712,10 @@
         <v>99.99</v>
       </c>
       <c r="U250" s="43" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="V250" s="43" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="X250" s="3" t="s">
         <v>158</v>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -5472,7 +5472,7 @@
     <t>1245</t>
   </si>
   <si>
-    <t>寂灭鸡王</t>
+    <t>鸿蒙鸡王</t>
   </si>
   <si>
     <t>1E+342</t>
@@ -5490,7 +5490,7 @@
     <t>1246</t>
   </si>
   <si>
-    <t>寂灭鹿王</t>
+    <t>鸿蒙鹿王</t>
   </si>
   <si>
     <t>1E+292</t>
@@ -5514,7 +5514,7 @@
     <t>1247</t>
   </si>
   <si>
-    <t>寂灭草王</t>
+    <t>鸿蒙草王</t>
   </si>
   <si>
     <t>1E+352</t>
@@ -5529,7 +5529,7 @@
     <t>1248</t>
   </si>
   <si>
-    <t>寂灭猫王</t>
+    <t>鸿蒙猫王</t>
   </si>
   <si>
     <t>1E+357</t>
@@ -5550,7 +5550,7 @@
     <t>1249</t>
   </si>
   <si>
-    <t>寂灭花王</t>
+    <t>鸿蒙花王</t>
   </si>
   <si>
     <t>1E+295</t>
@@ -5574,7 +5574,7 @@
     <t>1250</t>
   </si>
   <si>
-    <t>寂灭雪王</t>
+    <t>鸿蒙雪王</t>
   </si>
   <si>
     <t>1E+367</t>
@@ -5592,7 +5592,7 @@
     <t>1251</t>
   </si>
   <si>
-    <t>寂灭蝠王</t>
+    <t>鸿蒙蝠王</t>
   </si>
   <si>
     <t>1E+372</t>
@@ -5613,7 +5613,7 @@
     <t>1252</t>
   </si>
   <si>
-    <t>寂灭骷髅王</t>
+    <t>鸿蒙骷髅王</t>
   </si>
   <si>
     <t>1E+298</t>
@@ -5634,7 +5634,7 @@
     <t>1253</t>
   </si>
   <si>
-    <t>寂灭尸王</t>
+    <t>鸿蒙尸王</t>
   </si>
   <si>
     <t>1E+382</t>
@@ -5655,7 +5655,7 @@
     <t>1254</t>
   </si>
   <si>
-    <t>寂灭蛇王</t>
+    <t>鸿蒙蛇王</t>
   </si>
   <si>
     <t>1E+387</t>
@@ -5673,7 +5673,7 @@
     <t>1255</t>
   </si>
   <si>
-    <t>寂灭狼王</t>
+    <t>鸿蒙狼王</t>
   </si>
   <si>
     <t>1E+301</t>
@@ -5697,7 +5697,7 @@
     <t>1256</t>
   </si>
   <si>
-    <t>寂灭沙虫王</t>
+    <t>鸿蒙沙虫王</t>
   </si>
   <si>
     <t>1E+397</t>
@@ -5718,7 +5718,7 @@
     <t>1257</t>
   </si>
   <si>
-    <t>寂灭鹰王</t>
+    <t>鸿蒙鹰王</t>
   </si>
   <si>
     <t>1E+402</t>
@@ -5736,7 +5736,7 @@
     <t>1258</t>
   </si>
   <si>
-    <t>寂灭角虫王</t>
+    <t>鸿蒙角虫王</t>
   </si>
   <si>
     <t>1E+304</t>
@@ -5760,7 +5760,7 @@
     <t>1259</t>
   </si>
   <si>
-    <t>寂灭蜈蚣王</t>
+    <t>鸿蒙蜈蚣王</t>
   </si>
   <si>
     <t>1E+412</t>
@@ -5781,7 +5781,7 @@
     <t>1260</t>
   </si>
   <si>
-    <t>寂灭钳虫王</t>
+    <t>鸿蒙钳虫王</t>
   </si>
   <si>
     <t>1E+417</t>
@@ -5802,7 +5802,7 @@
     <t>1261</t>
   </si>
   <si>
-    <t>寂灭蠕虫王</t>
+    <t>鸿蒙蠕虫王</t>
   </si>
   <si>
     <t>1E+307</t>
@@ -5826,7 +5826,7 @@
     <t>1262</t>
   </si>
   <si>
-    <t>寂灭猪王</t>
+    <t>鸿蒙猪王</t>
   </si>
   <si>
     <t>1E+427</t>
@@ -5844,7 +5844,7 @@
     <t>1263</t>
   </si>
   <si>
-    <t>寂灭猪皇</t>
+    <t>鸿蒙猪皇</t>
   </si>
   <si>
     <t>1E+432</t>
@@ -5865,7 +5865,7 @@
     <t>1264</t>
   </si>
   <si>
-    <t>寂灭蝎王</t>
+    <t>鸿蒙蝎王</t>
   </si>
   <si>
     <t>1E+310</t>
@@ -5886,7 +5886,7 @@
     <t>1265</t>
   </si>
   <si>
-    <t>寂灭恶魔教主</t>
+    <t>鸿蒙恶魔教主</t>
   </si>
   <si>
     <t>1E+442</t>
@@ -5907,7 +5907,7 @@
     <t>1266</t>
   </si>
   <si>
-    <t>寂灭恶魔教皇</t>
+    <t>鸿蒙恶魔教皇</t>
   </si>
   <si>
     <t>1E+447</t>
@@ -5922,7 +5922,7 @@
     <t>1267</t>
   </si>
   <si>
-    <t>寂灭邪魔教主</t>
+    <t>鸿蒙邪魔教主</t>
   </si>
   <si>
     <t>1E+313</t>
@@ -5946,7 +5946,7 @@
     <t>1268</t>
   </si>
   <si>
-    <t>寂灭邪魔教皇</t>
+    <t>鸿蒙邪魔教皇</t>
   </si>
   <si>
     <t>1E+457</t>
@@ -5964,7 +5964,7 @@
     <t>1269</t>
   </si>
   <si>
-    <t>寂灭虹魔猪王</t>
+    <t>鸿蒙虹魔猪王</t>
   </si>
   <si>
     <t>1E+462</t>
@@ -5985,7 +5985,7 @@
     <t>1270</t>
   </si>
   <si>
-    <t>寂灭烈焰王</t>
+    <t>鸿蒙烈焰王</t>
   </si>
   <si>
     <t>1E+316</t>
@@ -6006,7 +6006,7 @@
     <t>1271</t>
   </si>
   <si>
-    <t>寂灭大邪王</t>
+    <t>鸿蒙大邪王</t>
   </si>
   <si>
     <t>1E+472</t>
@@ -6021,7 +6021,7 @@
     <t>1272</t>
   </si>
   <si>
-    <t>寂灭尸魔王</t>
+    <t>鸿蒙尸魔王</t>
   </si>
   <si>
     <t>1E+477</t>
@@ -6036,7 +6036,7 @@
     <t>1273</t>
   </si>
   <si>
-    <t>寂灭骨魔王</t>
+    <t>鸿蒙骨魔王</t>
   </si>
   <si>
     <t>1E+319</t>
@@ -6054,7 +6054,7 @@
     <t>1274</t>
   </si>
   <si>
-    <t>寂灭牛魔王</t>
+    <t>鸿蒙牛魔王</t>
   </si>
   <si>
     <t>1E+487</t>
@@ -6069,7 +6069,7 @@
     <t>1275</t>
   </si>
   <si>
-    <t>寂灭水龙王</t>
+    <t>鸿蒙水龙王</t>
   </si>
   <si>
     <t>1E+492</t>
@@ -6084,7 +6084,7 @@
     <t>1276</t>
   </si>
   <si>
-    <t>寂灭土龙王</t>
+    <t>鸿蒙土龙王</t>
   </si>
   <si>
     <t>1E+322</t>
@@ -6102,7 +6102,7 @@
     <t>1277</t>
   </si>
   <si>
-    <t>寂灭毒龙王</t>
+    <t>鸿蒙毒龙王</t>
   </si>
   <si>
     <t>1E+522</t>
@@ -6117,7 +6117,7 @@
     <t>1278</t>
   </si>
   <si>
-    <t>寂灭火龙王</t>
+    <t>鸿蒙火龙王</t>
   </si>
   <si>
     <t>1E+527</t>
@@ -6135,7 +6135,7 @@
     <t>1279</t>
   </si>
   <si>
-    <t>寂灭冰龙王</t>
+    <t>鸿蒙冰龙王</t>
   </si>
   <si>
     <t>1E+325</t>
@@ -6335,12 +6335,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
